--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484277_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484277_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>1.4121</v>
+        <v>0.8405</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0286</v>
+        <v>-0.6792</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3835</v>
+        <v>1.5196</v>
       </c>
       <c r="G2" t="n">
         <v>0.5591</v>
@@ -610,13 +610,13 @@
         <v>0.9767</v>
       </c>
       <c r="S2" t="n">
-        <v>0.853</v>
+        <v>0.2813</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5614</v>
+        <v>-0.1464</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2916</v>
+        <v>0.4277</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.151</v>
+        <v>0.4372</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6092</v>
+        <v>1.5687</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.4583</v>
+        <v>-1.1314</v>
       </c>
       <c r="G3" t="n">
         <v>1.2414</v>
@@ -688,13 +688,13 @@
         <v>1.5627</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7313</v>
+        <v>-0.4451</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1732</v>
+        <v>-0.2138</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5581</v>
+        <v>-0.2312</v>
       </c>
       <c r="V3" t="n">
         <v>-0.5545</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.3299</v>
+        <v>-0.0109</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4119</v>
+        <v>1.513</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.7418</v>
+        <v>-1.5239</v>
       </c>
       <c r="G4" t="n">
         <v>1.2631</v>
@@ -766,13 +766,13 @@
         <v>0.3907</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3994</v>
+        <v>-0.0805</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5447</v>
+        <v>-0.4436</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1453</v>
+        <v>0.3631</v>
       </c>
       <c r="V4" t="n">
         <v>-1.5842</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.535</v>
+        <v>-0.5272</v>
       </c>
       <c r="E5" t="n">
-        <v>1.9704</v>
+        <v>1.8693</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.5055</v>
+        <v>-2.3965</v>
       </c>
       <c r="G5" t="n">
         <v>0.3611</v>
@@ -844,13 +844,13 @@
         <v>1.1721</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1607</v>
+        <v>0.1685</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4153</v>
+        <v>-0.5164</v>
       </c>
       <c r="U5" t="n">
-        <v>0.576</v>
+        <v>0.6849</v>
       </c>
       <c r="V5" t="n">
         <v>-1.2521</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.8129999999999999</v>
+        <v>-1.0326</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0434</v>
+        <v>0.205</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8563</v>
+        <v>-1.2376</v>
       </c>
       <c r="G6" t="n">
         <v>-0.8917</v>
@@ -922,13 +922,13 @@
         <v>0.9767</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2024</v>
+        <v>-0.0172</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.6252</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9892</v>
+        <v>0.6079</v>
       </c>
       <c r="V6" t="n">
         <v>0.853</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.6382</v>
+        <v>-1.3465</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9107</v>
+        <v>-0.8096</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7275</v>
+        <v>-0.5368000000000001</v>
       </c>
       <c r="G7" t="n">
         <v>1.4983</v>
@@ -1000,13 +1000,13 @@
         <v>1.5627</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8826000000000001</v>
+        <v>-0.5908</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9078000000000001</v>
+        <v>-0.8067</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0253</v>
+        <v>0.2159</v>
       </c>
       <c r="V7" t="n">
         <v>-0.8865</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.2264</v>
+        <v>-2.0297</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6565</v>
+        <v>-1.596</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.57</v>
+        <v>-0.4338</v>
       </c>
       <c r="G8" t="n">
         <v>-0.2703</v>
@@ -1078,13 +1078,13 @@
         <v>0.9767</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9794</v>
+        <v>-0.7827</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6657</v>
+        <v>-0.6052</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3137</v>
+        <v>-0.1775</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.1703</v>
+        <v>-4.4537</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.0455</v>
+        <v>-3.3289</v>
       </c>
       <c r="F9" t="n">
         <v>-1.1248</v>
@@ -1156,10 +1156,10 @@
         <v>1.1721</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1678</v>
+        <v>-0.4512</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2337</v>
+        <v>-0.5172</v>
       </c>
       <c r="U9" t="n">
         <v>0.0659</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.6307</v>
+        <v>-4.5276</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.4084</v>
+        <v>-3.8423</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2223</v>
+        <v>-0.6853</v>
       </c>
       <c r="G10" t="n">
         <v>-3.1532</v>
@@ -1234,13 +1234,13 @@
         <v>1.1721</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0282</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0289</v>
+        <v>-0.4628</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0007</v>
+        <v>0.5377</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2772</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.6037</v>
+        <v>-4.9965</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.6579</v>
+        <v>-4.1324</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.9458</v>
+        <v>-0.8641</v>
       </c>
       <c r="G11" t="n">
         <v>-4.6753</v>
@@ -1312,13 +1312,13 @@
         <v>1.5627</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.401</v>
+        <v>-0.7938</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1499</v>
+        <v>-0.6244</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2511</v>
+        <v>-0.1694</v>
       </c>
       <c r="V11" t="n">
         <v>0.2772</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.0014</v>
+        <v>-6.1333</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.1679</v>
+        <v>-5.9457</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1665</v>
+        <v>-0.1876</v>
       </c>
       <c r="G12" t="n">
         <v>-3.2564</v>
@@ -1390,13 +1390,13 @@
         <v>1.1721</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2306</v>
+        <v>-0.3625</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9684</v>
+        <v>-0.7462</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7377</v>
+        <v>0.3837</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3656</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-24.3855</v>
+        <v>-23.7803</v>
       </c>
       <c r="E13" t="n">
-        <v>-15.7834</v>
+        <v>-15.1781</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.6023</v>
+        <v>-8.6022</v>
       </c>
       <c r="G13" t="n">
         <v>-9.859400000000001</v>
@@ -1468,13 +1468,13 @@
         <v>12.6973</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.6042</v>
+        <v>-2.9991</v>
       </c>
       <c r="T13" t="n">
-        <v>-6.313</v>
+        <v>-5.707899999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>2.7088</v>
+        <v>2.7087</v>
       </c>
       <c r="V13" t="n">
         <v>-6.0383</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.2468</v>
+        <v>6.0403</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4849</v>
+        <v>4.7883</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7618</v>
+        <v>1.2521</v>
       </c>
       <c r="G14" t="n">
         <v>7.0565</v>
@@ -1546,13 +1546,13 @@
         <v>1.7581</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3019</v>
+        <v>-0.5083</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1499</v>
+        <v>-0.8466</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1519</v>
+        <v>0.3383</v>
       </c>
       <c r="V14" t="n">
         <v>0.6642</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.0251</v>
+        <v>4.8889</v>
       </c>
       <c r="E15" t="n">
         <v>3.0461</v>
       </c>
       <c r="F15" t="n">
-        <v>1.979</v>
+        <v>1.8428</v>
       </c>
       <c r="G15" t="n">
         <v>3.1824</v>
@@ -1624,13 +1624,13 @@
         <v>1.5627</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9794</v>
+        <v>0.8431999999999999</v>
       </c>
       <c r="T15" t="n">
         <v>0.0689</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9106</v>
+        <v>0.7744</v>
       </c>
       <c r="V15" t="n">
         <v>0.2772</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.3699</v>
+        <v>4.6072</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8705</v>
+        <v>1.9716</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4995</v>
+        <v>2.6356</v>
       </c>
       <c r="G16" t="n">
         <v>3.1835</v>
@@ -1702,13 +1702,13 @@
         <v>1.7581</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4952</v>
+        <v>0.7325</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0083</v>
+        <v>0.1095</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4869</v>
+        <v>0.6231</v>
       </c>
       <c r="V16" t="n">
         <v>0.8865</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. CODINACHS PITA</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.7139</v>
+        <v>4.0147</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0275</v>
+        <v>1.5872</v>
       </c>
       <c r="F17" t="n">
-        <v>3.7415</v>
+        <v>2.4275</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1345</v>
+        <v>2.7356</v>
       </c>
       <c r="H17" t="n">
-        <v>1.2279</v>
+        <v>1.3062</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.3624</v>
+        <v>1.4293</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5284</v>
+        <v>2.3412</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6984</v>
+        <v>1.0463</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.2268</v>
+        <v>1.2949</v>
       </c>
       <c r="M17" t="n">
-        <v>0.394</v>
+        <v>0.3944</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5296</v>
+        <v>0.2599</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1356</v>
+        <v>0.1344</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7581</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S17" t="n">
-        <v>2.0903</v>
+        <v>0.4512</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5009</v>
+        <v>-0.0192</v>
       </c>
       <c r="U17" t="n">
-        <v>1.5894</v>
+        <v>0.4704</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>I. LLOVET CAMP</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.2834</v>
+        <v>2.8276</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1827</v>
+        <v>1.071</v>
       </c>
       <c r="F18" t="n">
-        <v>2.1007</v>
+        <v>1.7567</v>
       </c>
       <c r="G18" t="n">
-        <v>2.7356</v>
+        <v>1.183</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3062</v>
+        <v>2.5183</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4293</v>
+        <v>-1.3354</v>
       </c>
       <c r="J18" t="n">
-        <v>2.3412</v>
+        <v>1.9423</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0463</v>
+        <v>2.3331</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2949</v>
+        <v>-0.3908</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3944</v>
+        <v>-0.7593</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2599</v>
+        <v>0.1852</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1344</v>
+        <v>-0.9445</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.3907</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2801</v>
+        <v>1.0083</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4237</v>
+        <v>0.2504</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1436</v>
+        <v>0.7579</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2186</v>
+        <v>0.8317</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2186</v>
+        <v>0.8317</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. LLOVET CAMP</t>
+          <t>A. RUIZ CAÑAMERO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.6915</v>
+        <v>2.452</v>
       </c>
       <c r="E19" t="n">
-        <v>1.071</v>
+        <v>1.508</v>
       </c>
       <c r="F19" t="n">
-        <v>1.6205</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>1.183</v>
+        <v>3.403</v>
       </c>
       <c r="H19" t="n">
-        <v>2.5183</v>
+        <v>3.7271</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.3354</v>
+        <v>-0.3241</v>
       </c>
       <c r="J19" t="n">
-        <v>1.9423</v>
+        <v>3.6228</v>
       </c>
       <c r="K19" t="n">
-        <v>2.3331</v>
+        <v>3.5418</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.3908</v>
+        <v>0.0809</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7593</v>
+        <v>-0.2198</v>
       </c>
       <c r="N19" t="n">
         <v>0.1852</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9445</v>
+        <v>-0.4051</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
         <v>1.7581</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8722</v>
+        <v>-0.1816</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2504</v>
+        <v>-0.806</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6217</v>
+        <v>0.6244</v>
       </c>
       <c r="V19" t="n">
-        <v>0.8317</v>
+        <v>-1.5507</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8317</v>
+        <v>-0.3321</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. RUIZ CAÑAMERO</t>
+          <t>A. CODINACHS PITA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.3744</v>
+        <v>2.1346</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1035</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2709</v>
+        <v>2.87</v>
       </c>
       <c r="G20" t="n">
-        <v>3.403</v>
+        <v>-0.1345</v>
       </c>
       <c r="H20" t="n">
-        <v>3.7271</v>
+        <v>1.2279</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3241</v>
+        <v>-1.3624</v>
       </c>
       <c r="J20" t="n">
-        <v>3.6228</v>
+        <v>-0.5284</v>
       </c>
       <c r="K20" t="n">
-        <v>3.5418</v>
+        <v>0.6984</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0809</v>
+        <v>-1.2268</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2198</v>
+        <v>0.394</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1852</v>
+        <v>0.5296</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4051</v>
+        <v>-0.1356</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7814</v>
+        <v>1.7581</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>1.7581</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2592</v>
+        <v>0.511</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2105</v>
+        <v>-0.2069</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9512</v>
+        <v>0.7179</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.5507</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.0555</v>
+        <v>1.4604</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5825</v>
+        <v>0.178</v>
       </c>
       <c r="F21" t="n">
-        <v>1.473</v>
+        <v>1.2824</v>
       </c>
       <c r="G21" t="n">
         <v>-1.4079</v>
@@ -2092,13 +2092,13 @@
         <v>1.7581</v>
       </c>
       <c r="S21" t="n">
-        <v>1.7053</v>
+        <v>1.1102</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6219</v>
+        <v>0.2175</v>
       </c>
       <c r="U21" t="n">
-        <v>1.0834</v>
+        <v>0.8927</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.3824</v>
+        <v>1.2891</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6666</v>
+        <v>0.4644</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7158</v>
+        <v>0.8247</v>
       </c>
       <c r="G22" t="n">
         <v>-0.8683</v>
@@ -2170,13 +2170,13 @@
         <v>1.7581</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0814</v>
+        <v>-0.1747</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4153</v>
+        <v>-0.6175</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3339</v>
+        <v>0.4429</v>
       </c>
       <c r="V22" t="n">
         <v>1.5507</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.097</v>
+        <v>-2.0541</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.162</v>
+        <v>-3.3642</v>
       </c>
       <c r="F23" t="n">
-        <v>1.065</v>
+        <v>1.3101</v>
       </c>
       <c r="G23" t="n">
         <v>-2.3155</v>
@@ -2248,13 +2248,13 @@
         <v>1.5627</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3675</v>
+        <v>-0.3246</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3548</v>
+        <v>-0.5570000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0127</v>
+        <v>0.2324</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.6605</v>
+        <v>-3.2754</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.2161</v>
+        <v>-1.9128</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.4443</v>
+        <v>-1.3626</v>
       </c>
       <c r="G24" t="n">
         <v>-6.1584</v>
@@ -2326,13 +2326,13 @@
         <v>0.586</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2481</v>
+        <v>0.1369</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6052</v>
+        <v>-0.3019</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3571</v>
+        <v>0.4388</v>
       </c>
       <c r="V24" t="n">
         <v>2.16</v>
@@ -2359,25 +2359,25 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>24.3854</v>
+        <v>24.3853</v>
       </c>
       <c r="E25" t="n">
-        <v>8.6022</v>
+        <v>8.602199999999998</v>
       </c>
       <c r="F25" t="n">
         <v>15.7834</v>
       </c>
       <c r="G25" t="n">
-        <v>9.859399999999997</v>
+        <v>9.859400000000001</v>
       </c>
       <c r="H25" t="n">
         <v>11.8817</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.0223</v>
+        <v>-2.022300000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>17.80249999999999</v>
+        <v>17.8025</v>
       </c>
       <c r="K25" t="n">
         <v>11.7268</v>
@@ -2389,7 +2389,7 @@
         <v>-7.943000000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>0.1548999999999998</v>
+        <v>0.1549</v>
       </c>
       <c r="O25" t="n">
         <v>-8.098100000000001</v>
@@ -2404,13 +2404,13 @@
         <v>17.5808</v>
       </c>
       <c r="S25" t="n">
-        <v>3.604199999999999</v>
+        <v>3.6041</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.709</v>
+        <v>-2.7088</v>
       </c>
       <c r="U25" t="n">
-        <v>6.3132</v>
+        <v>6.313199999999999</v>
       </c>
       <c r="V25" t="n">
         <v>6.0382</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484277_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484277_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,74 +549,79 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>J. BERTOMEU BALDÉ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8405</v>
+        <v>0.914</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.6792</v>
+        <v>0.914</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5196</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5591</v>
+        <v>0.914</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.2095</v>
+        <v>0.307</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7687</v>
+        <v>0.607</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4439</v>
+        <v>0.914</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3492</v>
+        <v>0.307</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09470000000000001</v>
+        <v>0.607</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1152</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5587</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0.6739000000000001</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2813</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1464</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4277</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -626,447 +631,477 @@
       </c>
       <c r="X2" t="n">
         <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484277_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>J. LLORENTE GUILLEMI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4372</v>
+        <v>0.8405</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5687</v>
+        <v>-0.6792</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.1314</v>
+        <v>1.5196</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2414</v>
+        <v>0.5591</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5641</v>
+        <v>-0.2095</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.3227</v>
+        <v>0.7687</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1499</v>
+        <v>0.4439</v>
       </c>
       <c r="K3" t="n">
-        <v>2.988</v>
+        <v>0.3492</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1619</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.9085</v>
+        <v>0.1152</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4239</v>
+        <v>-0.5587</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.4846</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.3674</v>
+        <v>-0.9767</v>
       </c>
       <c r="R3" t="n">
-        <v>1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4451</v>
+        <v>0.2813</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2138</v>
+        <v>-0.1464</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2312</v>
+        <v>0.4277</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484277_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. FERRARI</t>
+          <t>E. MARTÍN GASCÓN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.0109</v>
+        <v>0.607</v>
       </c>
       <c r="E4" t="n">
-        <v>1.513</v>
+        <v>0.607</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.5239</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2631</v>
+        <v>0.607</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.057</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>2.3202</v>
+        <v>0.607</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9566</v>
+        <v>0.607</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0409</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9157</v>
+        <v>0.607</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6935</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.098</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4045</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0805</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4436</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3631</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.5842</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.5842</v>
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484277_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. GARCIA LOPEZ</t>
+          <t>R. DALET CASALPRIM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5272</v>
+        <v>0.4372</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8693</v>
+        <v>1.5687</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.3965</v>
+        <v>-1.1314</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3611</v>
+        <v>1.2414</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8391</v>
+        <v>2.5641</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2002</v>
+        <v>-1.3227</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3625</v>
+        <v>3.1499</v>
       </c>
       <c r="K5" t="n">
-        <v>0.6778999999999999</v>
+        <v>2.988</v>
       </c>
       <c r="L5" t="n">
-        <v>2.6846</v>
+        <v>0.1619</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.0014</v>
+        <v>-1.9085</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.517</v>
+        <v>-0.4239</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.4844</v>
+        <v>-1.4846</v>
       </c>
       <c r="P5" t="n">
         <v>0.1953</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9767</v>
+        <v>-1.3674</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1685</v>
+        <v>-0.4451</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5164</v>
+        <v>-0.2138</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6849</v>
+        <v>-0.2312</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2521</v>
+        <v>-0.5545</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2521</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484277_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>G. FERRARI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0326</v>
+        <v>-0.0109</v>
       </c>
       <c r="E6" t="n">
-        <v>0.205</v>
+        <v>1.513</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.2376</v>
+        <v>-1.5239</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8917</v>
+        <v>1.2631</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.2812</v>
+        <v>-1.057</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3895</v>
+        <v>2.3202</v>
       </c>
       <c r="J6" t="n">
-        <v>1.565</v>
+        <v>1.9566</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3646</v>
+        <v>0.0409</v>
       </c>
       <c r="L6" t="n">
-        <v>1.9295</v>
+        <v>1.9157</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.4567</v>
+        <v>-0.6935</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.9166</v>
+        <v>-1.098</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5401</v>
+        <v>0.4045</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0172</v>
+        <v>-0.0805</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6252</v>
+        <v>-0.4436</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6079</v>
+        <v>0.3631</v>
       </c>
       <c r="V6" t="n">
-        <v>0.853</v>
+        <v>-1.5842</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3656</v>
+        <v>-1.5842</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484277_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. BERTOMEU BALDÉ</t>
+          <t>M. GARCIA LOPEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3465</v>
+        <v>-0.5272</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8096</v>
+        <v>1.8693</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5368000000000001</v>
+        <v>-2.3965</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4983</v>
+        <v>0.3611</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4446</v>
+        <v>-0.8391</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0537</v>
+        <v>1.2002</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9272</v>
+        <v>3.3625</v>
       </c>
       <c r="K7" t="n">
-        <v>1.659</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2683</v>
+        <v>2.6846</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4289</v>
+        <v>-3.0014</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2144</v>
+        <v>-1.517</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2146</v>
+        <v>-1.4844</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5908</v>
+        <v>0.1685</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8067</v>
+        <v>-0.5164</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2159</v>
+        <v>0.6849</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.8865</v>
+        <v>-1.2521</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8865</v>
+        <v>-1.2521</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484277_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V. MANDIM SILVA</t>
+          <t>E. MARTIN GASCON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0297</v>
+        <v>-1.6396</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.596</v>
+        <v>-0.402</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4338</v>
+        <v>-1.2376</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2703</v>
+        <v>-1.4987</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3106</v>
+        <v>-2.2812</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0403</v>
+        <v>0.7825</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9627</v>
+        <v>0.958</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9222</v>
+        <v>-0.3646</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0405</v>
+        <v>1.3225</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.233</v>
+        <v>-2.4567</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2328</v>
+        <v>-1.9166</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0002</v>
+        <v>-0.5401</v>
       </c>
       <c r="P8" t="n">
         <v>-0.9767</v>
@@ -1078,574 +1113,610 @@
         <v>0.9767</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7827</v>
+        <v>-0.0172</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6052</v>
+        <v>-0.6252</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1775</v>
+        <v>0.6079</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.853</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.3656</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484277_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. GONZÁLEZ BRUMOS</t>
+          <t>V. MANDIM SILVA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.4537</v>
+        <v>-2.0297</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.3289</v>
+        <v>-1.596</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1248</v>
+        <v>-0.4338</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.5355</v>
+        <v>-0.2703</v>
       </c>
       <c r="H9" t="n">
-        <v>-3.6547</v>
+        <v>-0.3106</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1192</v>
+        <v>0.0403</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0928</v>
+        <v>0.9627</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.3472</v>
+        <v>0.9222</v>
       </c>
       <c r="L9" t="n">
-        <v>1.2544</v>
+        <v>0.0405</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4427</v>
+        <v>-1.233</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3075</v>
+        <v>-1.2328</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1352</v>
+        <v>-0.0002</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7814</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.3907</v>
+        <v>-1.9534</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4512</v>
+        <v>-0.7827</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5172</v>
+        <v>-0.6052</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0659</v>
+        <v>-0.1775</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.2484</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-1.3283</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.9201</v>
+        <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484277_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. PALOMARES MUÑOZ</t>
+          <t>J. BERTOMEU BALDE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.5276</v>
+        <v>-2.2604</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.8423</v>
+        <v>-1.7236</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6853</v>
+        <v>-0.5368000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.1532</v>
+        <v>0.5843</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2786</v>
+        <v>1.1376</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.8746</v>
+        <v>-0.5533</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.0354</v>
+        <v>2.0133</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5104</v>
+        <v>1.352</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5251</v>
+        <v>0.6613</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.1178</v>
+        <v>-1.4289</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7682</v>
+        <v>-0.2144</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.3496</v>
+        <v>-1.2146</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1721</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.3441</v>
+        <v>-2.9301</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S10" t="n">
-        <v>0.07489999999999999</v>
+        <v>-0.5908</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4628</v>
+        <v>-0.8067</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5377</v>
+        <v>0.2159</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2772</v>
+        <v>-0.8865</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2772</v>
+        <v>-0.8865</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484277_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>P. GONZALEZ BRUMOS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.9965</v>
+        <v>-4.4537</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.1324</v>
+        <v>-3.3289</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8641</v>
+        <v>-1.1248</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.6753</v>
+        <v>-2.5355</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.4621</v>
+        <v>-3.6547</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.2132</v>
+        <v>1.1192</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.4178</v>
+        <v>-1.0928</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.2845</v>
+        <v>-2.3472</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1332</v>
+        <v>1.2544</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.2575</v>
+        <v>-1.4427</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.1775</v>
+        <v>-1.3075</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.0799</v>
+        <v>-0.1352</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.3674</v>
+        <v>-0.3907</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7938</v>
+        <v>-0.4512</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6244</v>
+        <v>-0.5172</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1694</v>
+        <v>0.0659</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2772</v>
+        <v>-2.2484</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2772</v>
+        <v>-1.3283</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.9201</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484277_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. FONTANALS MARTIN</t>
+          <t>R. PALOMARES MUNOZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.1333</v>
+        <v>-4.5276</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.9457</v>
+        <v>-3.8423</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1876</v>
+        <v>-0.6853</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.2564</v>
+        <v>-3.1532</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.7977</v>
+        <v>-1.2786</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.4587</v>
+        <v>-1.8746</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.8787</v>
+        <v>-1.0354</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.2855</v>
+        <v>-0.5104</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5931999999999999</v>
+        <v>-0.5251</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.3777</v>
+        <v>-2.1178</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.5121</v>
+        <v>-0.7682</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1344</v>
+        <v>-1.3496</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.1488</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.3208</v>
+        <v>-2.3441</v>
       </c>
       <c r="R12" t="n">
         <v>1.1721</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3625</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7462</v>
+        <v>-0.4628</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3837</v>
+        <v>0.5377</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3656</v>
+        <v>-0.2772</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.3656</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484277_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>R. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-23.7803</v>
+        <v>-4.9965</v>
       </c>
       <c r="E13" t="n">
-        <v>-15.1781</v>
+        <v>-4.1324</v>
       </c>
       <c r="F13" t="n">
-        <v>-8.6022</v>
+        <v>-0.8641</v>
       </c>
       <c r="G13" t="n">
-        <v>-9.859400000000001</v>
+        <v>-4.6753</v>
       </c>
       <c r="H13" t="n">
-        <v>-11.8818</v>
+        <v>-3.4621</v>
       </c>
       <c r="I13" t="n">
-        <v>2.0226</v>
+        <v>-1.2132</v>
       </c>
       <c r="J13" t="n">
-        <v>7.943100000000003</v>
+        <v>-2.4178</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.155</v>
+        <v>-2.2845</v>
       </c>
       <c r="L13" t="n">
-        <v>8.098099999999999</v>
+        <v>-0.1332</v>
       </c>
       <c r="M13" t="n">
-        <v>-17.8025</v>
+        <v>-2.2575</v>
       </c>
       <c r="N13" t="n">
-        <v>-11.7267</v>
+        <v>-1.1775</v>
       </c>
       <c r="O13" t="n">
-        <v>-6.075799999999999</v>
+        <v>-1.0799</v>
       </c>
       <c r="P13" t="n">
-        <v>-4.8837</v>
+        <v>0.1953</v>
       </c>
       <c r="Q13" t="n">
-        <v>-17.5807</v>
+        <v>-1.3674</v>
       </c>
       <c r="R13" t="n">
-        <v>12.6973</v>
+        <v>1.5627</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.9991</v>
+        <v>-0.7938</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.707899999999999</v>
+        <v>-0.6244</v>
       </c>
       <c r="U13" t="n">
-        <v>2.7087</v>
+        <v>-0.1694</v>
       </c>
       <c r="V13" t="n">
-        <v>-6.0383</v>
+        <v>0.2772</v>
       </c>
       <c r="W13" t="n">
-        <v>0.1674999999999999</v>
+        <v>0.2772</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.2058</v>
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484277_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>M. FONTANALS MARTIN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TQ-CB PRAT</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.0403</v>
+        <v>-6.1333</v>
       </c>
       <c r="E14" t="n">
-        <v>4.7883</v>
+        <v>-5.9457</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2521</v>
+        <v>-0.1876</v>
       </c>
       <c r="G14" t="n">
-        <v>7.0565</v>
+        <v>-3.2564</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4047</v>
+        <v>-2.7977</v>
       </c>
       <c r="I14" t="n">
-        <v>5.6518</v>
+        <v>-0.4587</v>
       </c>
       <c r="J14" t="n">
-        <v>8.565</v>
+        <v>-1.8787</v>
       </c>
       <c r="K14" t="n">
-        <v>1.6987</v>
+        <v>-1.2855</v>
       </c>
       <c r="L14" t="n">
-        <v>6.8663</v>
+        <v>-0.5931999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.5085</v>
+        <v>-1.3777</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2939</v>
+        <v>-1.5121</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.2146</v>
+        <v>0.1344</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.1721</v>
+        <v>-2.1488</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.9301</v>
+        <v>-3.3208</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7581</v>
+        <v>1.1721</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5083</v>
+        <v>-0.3625</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8466</v>
+        <v>-0.7462</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3383</v>
+        <v>0.3837</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6642</v>
+        <v>-0.3656</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6642</v>
+        <v>-0.3656</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484277_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TQ-CB PRAT</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.8889</v>
+        <v>-23.7802</v>
       </c>
       <c r="E15" t="n">
-        <v>3.0461</v>
+        <v>-15.1781</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8428</v>
+        <v>-8.6022</v>
       </c>
       <c r="G15" t="n">
-        <v>3.1824</v>
+        <v>-9.859400000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>2.7243</v>
+        <v>-11.8818</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4582</v>
+        <v>2.0226</v>
       </c>
       <c r="J15" t="n">
-        <v>3.6767</v>
+        <v>7.943199999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>2.9483</v>
+        <v>-0.1549999999999991</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7284</v>
+        <v>8.098100000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4943</v>
+        <v>-17.8025</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2241</v>
+        <v>-11.7267</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2702</v>
+        <v>-6.075799999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>0.586</v>
+        <v>-4.883699999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>-17.5807</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5627</v>
+        <v>12.6973</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8431999999999999</v>
+        <v>-2.9991</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0689</v>
+        <v>-5.707899999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7744</v>
+        <v>2.7087</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2772</v>
+        <v>-6.0383</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2772</v>
+        <v>0.1674999999999999</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
-      </c>
+        <v>-6.205799999999999</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. CARRASCO SAGRISTA</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.6072</v>
+        <v>4.8889</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9716</v>
+        <v>3.0461</v>
       </c>
       <c r="F16" t="n">
-        <v>2.6356</v>
+        <v>1.8428</v>
       </c>
       <c r="G16" t="n">
-        <v>3.1835</v>
+        <v>3.1824</v>
       </c>
       <c r="H16" t="n">
-        <v>3.0348</v>
+        <v>2.7243</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1486</v>
+        <v>0.4582</v>
       </c>
       <c r="J16" t="n">
-        <v>2.929</v>
+        <v>3.6767</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3753</v>
+        <v>2.9483</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5537</v>
+        <v>0.7284</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2545</v>
+        <v>-0.4943</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6595</v>
+        <v>-0.2241</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4051</v>
+        <v>-0.2702</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1953</v>
+        <v>0.586</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7325</v>
+        <v>0.8431999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1095</v>
+        <v>0.0689</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6231</v>
+        <v>0.7744</v>
       </c>
       <c r="V16" t="n">
-        <v>0.8865</v>
+        <v>0.2772</v>
       </c>
       <c r="W16" t="n">
-        <v>0.8865</v>
+        <v>0.2772</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484277_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>R. CARRASCO SAGRISTA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.0147</v>
+        <v>4.6072</v>
       </c>
       <c r="E17" t="n">
-        <v>1.5872</v>
+        <v>1.9716</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4275</v>
+        <v>2.6356</v>
       </c>
       <c r="G17" t="n">
-        <v>2.7356</v>
+        <v>3.1835</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3062</v>
+        <v>3.0348</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4293</v>
+        <v>0.1486</v>
       </c>
       <c r="J17" t="n">
-        <v>2.3412</v>
+        <v>2.929</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0463</v>
+        <v>2.3753</v>
       </c>
       <c r="L17" t="n">
-        <v>1.2949</v>
+        <v>0.5537</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3944</v>
+        <v>0.2545</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2599</v>
+        <v>0.6595</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1344</v>
+        <v>-0.4051</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3907</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q17" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>0.4512</v>
+        <v>0.7325</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0192</v>
+        <v>0.1095</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4704</v>
+        <v>0.6231</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2186</v>
+        <v>0.8865</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2186</v>
+        <v>0.8865</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484277_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>I. LLOVET CAMP</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.8276</v>
+        <v>4.0147</v>
       </c>
       <c r="E18" t="n">
-        <v>1.071</v>
+        <v>1.5872</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7567</v>
+        <v>2.4275</v>
       </c>
       <c r="G18" t="n">
-        <v>1.183</v>
+        <v>2.7356</v>
       </c>
       <c r="H18" t="n">
-        <v>2.5183</v>
+        <v>1.3062</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3354</v>
+        <v>1.4293</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9423</v>
+        <v>2.3412</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3331</v>
+        <v>1.0463</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.3908</v>
+        <v>1.2949</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7593</v>
+        <v>0.3944</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1852</v>
+        <v>0.2599</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.9445</v>
+        <v>0.1344</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q18" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7581</v>
+        <v>1.5627</v>
       </c>
       <c r="S18" t="n">
-        <v>1.0083</v>
+        <v>0.4512</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2504</v>
+        <v>-0.0192</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7579</v>
+        <v>0.4704</v>
       </c>
       <c r="V18" t="n">
-        <v>0.8317</v>
+        <v>1.2186</v>
       </c>
       <c r="W18" t="n">
-        <v>0.8317</v>
+        <v>1.2186</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484277_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. RUIZ CAÑAMERO</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.452</v>
+        <v>3.6489</v>
       </c>
       <c r="E19" t="n">
-        <v>1.508</v>
+        <v>3.6489</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9441000000000001</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>3.403</v>
+        <v>3.6489</v>
       </c>
       <c r="H19" t="n">
-        <v>3.7271</v>
+        <v>0.614</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.3241</v>
+        <v>3.0349</v>
       </c>
       <c r="J19" t="n">
-        <v>3.6228</v>
+        <v>3.6489</v>
       </c>
       <c r="K19" t="n">
-        <v>3.5418</v>
+        <v>0.614</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0809</v>
+        <v>3.0349</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2198</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1852</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4051</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1816</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.806</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>0.6244</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.5507</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484277_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. CODINACHS PITA</t>
+          <t>I. LLOVET CAMP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.1346</v>
+        <v>2.8276</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7354000000000001</v>
+        <v>1.071</v>
       </c>
       <c r="F20" t="n">
-        <v>2.87</v>
+        <v>1.7567</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1345</v>
+        <v>1.183</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2279</v>
+        <v>2.5183</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3624</v>
+        <v>-1.3354</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5284</v>
+        <v>1.9423</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6984</v>
+        <v>2.3331</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2268</v>
+        <v>-0.3908</v>
       </c>
       <c r="M20" t="n">
-        <v>0.394</v>
+        <v>-0.7593</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5296</v>
+        <v>0.1852</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1356</v>
+        <v>-0.9445</v>
       </c>
       <c r="P20" t="n">
-        <v>1.7581</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R20" t="n">
         <v>1.7581</v>
       </c>
       <c r="S20" t="n">
-        <v>0.511</v>
+        <v>1.0083</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2069</v>
+        <v>0.2504</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7179</v>
+        <v>0.7579</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.8317</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.8317</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484277_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. OMOARUNA OSAZUWA</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.4604</v>
+        <v>2.3914</v>
       </c>
       <c r="E21" t="n">
-        <v>0.178</v>
+        <v>1.1394</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2824</v>
+        <v>1.2521</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4079</v>
+        <v>3.4076</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1433</v>
+        <v>0.7907999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5511</v>
+        <v>2.6168</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0395</v>
+        <v>4.9161</v>
       </c>
       <c r="K21" t="n">
-        <v>0.4323</v>
+        <v>1.0847</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.4718</v>
+        <v>3.8314</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.3684</v>
+        <v>-1.5085</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2891</v>
+        <v>-0.2939</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0793</v>
+        <v>-1.2146</v>
       </c>
       <c r="P21" t="n">
-        <v>1.7581</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.9301</v>
       </c>
       <c r="R21" t="n">
         <v>1.7581</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1102</v>
+        <v>-0.5083</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2175</v>
+        <v>-0.8466</v>
       </c>
       <c r="U21" t="n">
-        <v>0.8927</v>
+        <v>0.3383</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.6642</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484277_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. SESE FRASNEDO</t>
+          <t>A. RUIZ CANAMERO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,40 +2226,40 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.2891</v>
+        <v>2.1451</v>
       </c>
       <c r="E22" t="n">
-        <v>0.4644</v>
+        <v>1.201</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8247</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8683</v>
+        <v>3.096</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.0714</v>
+        <v>3.4201</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2031</v>
+        <v>-0.3241</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2307</v>
+        <v>3.3158</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.9171</v>
+        <v>3.2349</v>
       </c>
       <c r="L22" t="n">
-        <v>1.1478</v>
+        <v>0.0809</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.099</v>
+        <v>-0.2198</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.1542</v>
+        <v>0.1852</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.9447</v>
+        <v>-0.4051</v>
       </c>
       <c r="P22" t="n">
         <v>0.7814</v>
@@ -2170,28 +2271,33 @@
         <v>1.7581</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1747</v>
+        <v>-0.1816</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6175</v>
+        <v>-0.806</v>
       </c>
       <c r="U22" t="n">
-        <v>0.4429</v>
+        <v>0.6244</v>
       </c>
       <c r="V22" t="n">
-        <v>1.5507</v>
+        <v>-1.5507</v>
       </c>
       <c r="W22" t="n">
-        <v>1.8279</v>
+        <v>-0.3321</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484277_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. NOGUES JARNE</t>
+          <t>A. CODINACHS PITA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,58 +2309,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.0541</v>
+        <v>2.1346</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3642</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3101</v>
+        <v>2.87</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.3155</v>
+        <v>-0.1345</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.6275</v>
+        <v>1.2279</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6879</v>
+        <v>-1.3624</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.8305</v>
+        <v>-0.5284</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.8176</v>
+        <v>0.6984</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.0128</v>
+        <v>-1.2268</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.485</v>
+        <v>0.394</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1901</v>
+        <v>0.5296</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6751</v>
+        <v>-0.1356</v>
       </c>
       <c r="P23" t="n">
-        <v>0.586</v>
+        <v>1.7581</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3246</v>
+        <v>0.511</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5570000000000001</v>
+        <v>-0.2069</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2324</v>
+        <v>0.7179</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2264,12 +2370,17 @@
       </c>
       <c r="X23" t="n">
         <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484277_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>I. MACÍAS MERINO</t>
+          <t>J. OMOARUNA OSAZUWA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2754</v>
+        <v>1.4604</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.9128</v>
+        <v>0.178</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3626</v>
+        <v>1.2824</v>
       </c>
       <c r="G24" t="n">
-        <v>-6.1584</v>
+        <v>-1.4079</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.506</v>
+        <v>0.1433</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.6524</v>
+        <v>-1.5511</v>
       </c>
       <c r="J24" t="n">
-        <v>-3.1068</v>
+        <v>-0.0395</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6127</v>
+        <v>0.4323</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.4941</v>
+        <v>-0.4718</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.0516</v>
+        <v>-1.3684</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8933</v>
+        <v>-0.2891</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.1583</v>
+        <v>-1.0793</v>
       </c>
       <c r="P24" t="n">
-        <v>0.586</v>
+        <v>1.7581</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.586</v>
+        <v>1.7581</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1369</v>
+        <v>1.1102</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3019</v>
+        <v>0.2175</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4388</v>
+        <v>0.8927</v>
       </c>
       <c r="V24" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0.6642</v>
+        <v>0</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484277_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. SESE FRASNEDO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,68 +2475,401 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>24.3853</v>
+        <v>1.2891</v>
       </c>
       <c r="E25" t="n">
+        <v>0.4644</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.8247</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-0.8683</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-1.0714</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.2031</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.2307</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.9171</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.1478</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-1.099</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.1542</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.9447</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.1747</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.6175</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.4429</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.5507</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.8279</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484277_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A. RUIZ CAÑAMERO</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TQ-CB PRAT</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484277_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>J. NOGUES JARNE</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TQ-CB PRAT</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-2.0541</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-3.3642</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.3101</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-2.3155</v>
+      </c>
+      <c r="H27" t="n">
+        <v>-1.6275</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-0.6879</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-1.8305</v>
+      </c>
+      <c r="K27" t="n">
+        <v>-1.8176</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-0.0128</v>
+      </c>
+      <c r="M27" t="n">
+        <v>-0.485</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.1901</v>
+      </c>
+      <c r="O27" t="n">
+        <v>-0.6751</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-0.3246</v>
+      </c>
+      <c r="T27" t="n">
+        <v>-0.5570000000000001</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.2324</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>play_by_play_2484277_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>I. MACIAS MERINO</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TQ-CB PRAT</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-3.2754</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-1.9128</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-1.3626</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-6.1584</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-1.506</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-4.6524</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-3.1068</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-0.6127</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-2.4941</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-3.0516</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-0.8933</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-2.1583</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.1369</v>
+      </c>
+      <c r="T28" t="n">
+        <v>-0.3019</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.4388</v>
+      </c>
+      <c r="V28" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.4959</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0.6642</v>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>play_by_play_2484277_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>TQ-CB PRAT</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>24.3854</v>
+      </c>
+      <c r="E29" t="n">
         <v>8.602199999999998</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F29" t="n">
         <v>15.7834</v>
       </c>
-      <c r="G25" t="n">
-        <v>9.859400000000001</v>
-      </c>
-      <c r="H25" t="n">
-        <v>11.8817</v>
-      </c>
-      <c r="I25" t="n">
-        <v>-2.022300000000001</v>
-      </c>
-      <c r="J25" t="n">
-        <v>17.8025</v>
-      </c>
-      <c r="K25" t="n">
-        <v>11.7268</v>
-      </c>
-      <c r="L25" t="n">
+      <c r="G29" t="n">
+        <v>9.859399999999994</v>
+      </c>
+      <c r="H29" t="n">
+        <v>11.8818</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-2.0224</v>
+      </c>
+      <c r="J29" t="n">
+        <v>17.80249999999999</v>
+      </c>
+      <c r="K29" t="n">
+        <v>11.7269</v>
+      </c>
+      <c r="L29" t="n">
         <v>6.075699999999999</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M29" t="n">
         <v>-7.943000000000001</v>
       </c>
-      <c r="N25" t="n">
-        <v>0.1549</v>
-      </c>
-      <c r="O25" t="n">
+      <c r="N29" t="n">
+        <v>0.1549000000000003</v>
+      </c>
+      <c r="O29" t="n">
         <v>-8.098100000000001</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P29" t="n">
         <v>4.8836</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q29" t="n">
         <v>-12.6971</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R29" t="n">
         <v>17.5808</v>
       </c>
-      <c r="S25" t="n">
+      <c r="S29" t="n">
         <v>3.6041</v>
       </c>
-      <c r="T25" t="n">
+      <c r="T29" t="n">
         <v>-2.7088</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U29" t="n">
         <v>6.313199999999999</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V29" t="n">
         <v>6.0382</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W29" t="n">
         <v>6.205699999999999</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X29" t="n">
         <v>-0.1673999999999999</v>
       </c>
+      <c r="Y29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
